--- a/data/research/model_ledgers/rainbow-six-tiered-elo.xlsx
+++ b/data/research/model_ledgers/rainbow-six-tiered-elo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:AJ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -860,8 +860,836 @@
       <c r="AI3" s="2" t="inlineStr"/>
       <c r="AJ3" s="2" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>7ad62c8fc5a6471b</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>a698c67f693c2eeab5e359d6ca252b9aa5ba235175563e8abf0dff8043e8288c</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>73419</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0.578429</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>0.03925849308755758</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:30:27.416067Z</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:20:00Z</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:56:44.207613Z</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AG4" s="2" t="inlineStr"/>
+      <c r="AH4" s="2" t="inlineStr"/>
+      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>1faf1668ae154287</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>90976dc6def9b79d6ded6f0d9b84032e55b3da778f9640d6530362838eceb35f</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>73800</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0.565101</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>0.0458702307692308</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:04.146684Z</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>1a302d6bb4dd41bc</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>90976dc6def9b79d6ded6f0d9b84032e55b3da778f9640d6530362838eceb35f</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>74105</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0.706556</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>0.03658900330032999</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:06.111217Z</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>4c593951973e4011</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>cdeb49dc54d4b74458e45681b9eab51cf9a0d78593b5d92cf5a36ef28d8b5e83</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>73798</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0.547586</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>0.06681676923076929</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:20.503959Z</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>3310aea411ee4b83</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>cdeb49dc54d4b74458e45681b9eab51cf9a0d78593b5d92cf5a36ef28d8b5e83</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>74105</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0.706371</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>0.025859817891373815</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:24.552843Z</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>7800f8b346024395</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>dcbea0d6e44a197d151ad8db75722d635d4d0bd7bd09e144da986540255bdce7</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>73800</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0.564874</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>0.03435756807511736</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:12.460618Z</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>27940d3839ab400d</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>dcbea0d6e44a197d151ad8db75722d635d4d0bd7bd09e144da986540255bdce7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>74105</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0.706186</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>0.04632205442176862</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:14.310424Z</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>73a841eb072e4f18</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>76678b41de86b4af53a98d1bd306b91cd2e1d1a962dde1ac15820c6ae3d5cf10</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>73800</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0.56476</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>0.034243568075117414</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:54.466472Z</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ3"/>
+  <autoFilter ref="A1:AJ11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/rainbow-six-tiered-elo.xlsx
+++ b/data/research/model_ledgers/rainbow-six-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ11"/>
+  <dimension ref="A1:AJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1688,8 +1688,110 @@
       <c r="AI11" s="2" t="inlineStr"/>
       <c r="AJ11" s="2" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>8d61de2dd57d4791</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>a1186963418d35e4bf82cf39edb5ff26b515ca7bbe4df48b68c177a2080e2747</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>73800</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0.564286</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>0.05448207843137254</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:07.415025Z</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ11"/>
+  <autoFilter ref="A1:AJ12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/rainbow-six-tiered-elo.xlsx
+++ b/data/research/model_ledgers/rainbow-six-tiered-elo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:AJ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -860,8 +860,2896 @@
       <c r="AI3" s="2" t="inlineStr"/>
       <c r="AJ3" s="2" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>7ad62c8fc5a6471b</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>a698c67f693c2eeab5e359d6ca252b9aa5ba235175563e8abf0dff8043e8288c</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>73419</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0.578429</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>0.03925849308755758</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:30:27.416067Z</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:20:00Z</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:56:44.207613Z</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AG4" s="2" t="inlineStr"/>
+      <c r="AH4" s="2" t="inlineStr"/>
+      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>1faf1668ae154287</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>90976dc6def9b79d6ded6f0d9b84032e55b3da778f9640d6530362838eceb35f</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>73800</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0.565101</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>0.0458702307692308</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:04.146684Z</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>1a302d6bb4dd41bc</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>90976dc6def9b79d6ded6f0d9b84032e55b3da778f9640d6530362838eceb35f</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>74105</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0.706556</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>0.03658900330032999</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:06.111217Z</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>4c593951973e4011</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>cdeb49dc54d4b74458e45681b9eab51cf9a0d78593b5d92cf5a36ef28d8b5e83</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>73798</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0.547586</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>0.06681676923076929</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:20.503959Z</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>3310aea411ee4b83</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>cdeb49dc54d4b74458e45681b9eab51cf9a0d78593b5d92cf5a36ef28d8b5e83</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>74105</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0.706371</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>0.025859817891373815</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:24.552843Z</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>7800f8b346024395</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>dcbea0d6e44a197d151ad8db75722d635d4d0bd7bd09e144da986540255bdce7</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>73800</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0.564874</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>0.03435756807511736</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:12.460618Z</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>27940d3839ab400d</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>dcbea0d6e44a197d151ad8db75722d635d4d0bd7bd09e144da986540255bdce7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>74105</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0.706186</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>0.04632205442176862</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:17:14.310424Z</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>73a841eb072e4f18</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>76678b41de86b4af53a98d1bd306b91cd2e1d1a962dde1ac15820c6ae3d5cf10</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>73800</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0.56476</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>0.034243568075117414</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:54.466472Z</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>8d61de2dd57d4791</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>a1186963418d35e4bf82cf39edb5ff26b515ca7bbe4df48b68c177a2080e2747</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>73800</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0.564286</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>0.05448207843137254</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:07.415025Z</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>c8102dd965c04bea</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1736daa2e1da03e12c6835e4b0a2910e14046efe64fc9b405df50bf6aaac6c3b</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>73800</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0.564141</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>0.05433707843137259</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:07:51.474953Z</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>59f361552764486f</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3b81c1a225385446e6c2efcb53bbcef49ca7c03c0ccb69faec9e458b1a6f00c1</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>75283</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0.582007</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>0.20177886311787074</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T14:01:43.349448Z</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>0.360000</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>-0.020228</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>2.0375</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T17:05:13.671770Z</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>d6b7db316a314d52</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>e83a3ac7069db9030b6e73562e1d182c7126691e9608825d6879cd3d08d6102b</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>76934</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0.63019</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>0.03018999999999994</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11T19:58:25.883751Z</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>d3556e9c0edf469b</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>683507eb972ca2dde1f3ed76f99a039559c55d63946164b3366f174f8e38632a</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>76934</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0.630084</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>0.020708999999999977</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11T23:03:46.758426Z</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr"/>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>053f587ae6ca4c41</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5927380effc0fd200d8f5ee707e04a74e0ab76a027aecbe00226842cba129b19</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>76934</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0.629976</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>0.03981206557377048</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T02:10:02.145114Z</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr"/>
+      <c r="AI17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>4063a4f17bc64219</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5927380effc0fd200d8f5ee707e04a74e0ab76a027aecbe00226842cba129b19</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>76937</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0.507008</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>0.10700799999999999</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T02:10:02.626995Z</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>4ab11c68d25f4f86</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>a247738f7e3a05afd3824b27a7df4c07a881cca13a81c1e3a5155a97c016e160</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>76937</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0.506959</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0.37037037037037035</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>0.1365886296296297</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:16:07.833051Z</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr"/>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>992ca24552364a63</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>a247738f7e3a05afd3824b27a7df4c07a881cca13a81c1e3a5155a97c016e160</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>77319</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0.645071</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>0.02529913688212926</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:16:08.793606Z</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AG20" s="2" t="inlineStr"/>
+      <c r="AH20" s="2" t="inlineStr"/>
+      <c r="AI20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>a660355349444dd9</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>a247738f7e3a05afd3824b27a7df4c07a881cca13a81c1e3a5155a97c016e160</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>77480</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0.740676</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>0.10038823021582732</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:16:09.447658Z</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2eb63c8224074d73</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>6f58fd90e08e64d0a58042eeb19a26a1debe889dbb200a082a99f51d84977c3b</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>76937</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0.506911</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0.3597122302158273</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>0.14719876978417268</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:22:24.211191Z</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr"/>
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>9b8e04b7e58d4f7e</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>6f58fd90e08e64d0a58042eeb19a26a1debe889dbb200a082a99f51d84977c3b</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>77319</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0.644944</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>0.02517213688212927</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:22:24.701853Z</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr"/>
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AG23" s="2" t="inlineStr"/>
+      <c r="AH23" s="2" t="inlineStr"/>
+      <c r="AI23" s="2" t="inlineStr"/>
+      <c r="AJ23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>8d1e67060c164ec4</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>6f58fd90e08e64d0a58042eeb19a26a1debe889dbb200a082a99f51d84977c3b</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>77480</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0.740471</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>0.11084137037037045</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:22:25.426868Z</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr"/>
+      <c r="AE24" s="2" t="inlineStr"/>
+      <c r="AF24" s="2" t="inlineStr"/>
+      <c r="AG24" s="2" t="inlineStr"/>
+      <c r="AH24" s="2" t="inlineStr"/>
+      <c r="AI24" s="2" t="inlineStr"/>
+      <c r="AJ24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>3e3e5562cee04200</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>7374b813c568939dd2dea90ed4c12ad78e24834117de140d0ad4d70bf9edd602</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>77319</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0.644818</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>0.0045302302158273244</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T11:30:04.028629Z</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr"/>
+      <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AG25" s="2" t="inlineStr"/>
+      <c r="AH25" s="2" t="inlineStr"/>
+      <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>0ebd6e2a9a774c1b</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>7374b813c568939dd2dea90ed4c12ad78e24834117de140d0ad4d70bf9edd602</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>77480</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0.740265</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>0.11063537037037041</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T11:30:04.536403Z</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr"/>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AG26" s="2" t="inlineStr"/>
+      <c r="AH26" s="2" t="inlineStr"/>
+      <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>c3545c9d975c483f</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>ff702d2b685aebbdebd0127911b99b1822bd9d311c75192655ecfe2c55fcb8bc</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>76937</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0.506813</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>0.0866449327731092</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T14:37:09.739415Z</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr"/>
+      <c r="AE27" s="2" t="inlineStr"/>
+      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AG27" s="2" t="inlineStr"/>
+      <c r="AH27" s="2" t="inlineStr"/>
+      <c r="AI27" s="2" t="inlineStr"/>
+      <c r="AJ27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ed8285679b5f4595</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>ff702d2b685aebbdebd0127911b99b1822bd9d311c75192655ecfe2c55fcb8bc</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>77319</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0.644691</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>0.004403230215827336</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T14:37:10.209992Z</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr"/>
+      <c r="AE28" s="2" t="inlineStr"/>
+      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AG28" s="2" t="inlineStr"/>
+      <c r="AH28" s="2" t="inlineStr"/>
+      <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>c59fcd65ada740f5</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>ff702d2b685aebbdebd0127911b99b1822bd9d311c75192655ecfe2c55fcb8bc</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>77480</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0.74006</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>0.12028813688212936</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T14:37:10.720917Z</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr"/>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr"/>
+      <c r="AE29" s="2" t="inlineStr"/>
+      <c r="AF29" s="2" t="inlineStr"/>
+      <c r="AG29" s="2" t="inlineStr"/>
+      <c r="AH29" s="2" t="inlineStr"/>
+      <c r="AI29" s="2" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>5dd14a15b512472b</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>815cb088e917b6a7c0f8a38d775d446292769b4ccda7155204e46f86c22c3711</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>77319</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0.644606</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>0.014976370370370473</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T16:44:43.443038Z</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr"/>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr"/>
+      <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr"/>
+      <c r="AG30" s="2" t="inlineStr"/>
+      <c r="AH30" s="2" t="inlineStr"/>
+      <c r="AI30" s="2" t="inlineStr"/>
+      <c r="AJ30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>d46197ccab4840f3</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>815cb088e917b6a7c0f8a38d775d446292769b4ccda7155204e46f86c22c3711</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>77480</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>0.73992</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>0.12014813688212933</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T16:44:43.930162Z</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="2" t="inlineStr"/>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr"/>
+      <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr"/>
+      <c r="AG31" s="2" t="inlineStr"/>
+      <c r="AH31" s="2" t="inlineStr"/>
+      <c r="AI31" s="2" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ3"/>
+  <autoFilter ref="A1:AJ31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>